--- a/app/tests/subscription_export.xlsx
+++ b/app/tests/subscription_export.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>TAX</t>
+          <t>vat</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-03 14:16:55</t>
+          <t>2026-03-19 10:02:33</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -480,20 +480,20 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="E2" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>1200</v>
       </c>
       <c r="G2" t="n">
-        <v>7.5</v>
+        <v>1200</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-11-05 14:16:55</t>
+          <t>2026-03-21 10:02:33</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -515,20 +515,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="E3" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1200</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>

--- a/app/tests/subscription_export.xlsx
+++ b/app/tests/subscription_export.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-19 10:02:33</t>
+          <t>2026-03-19 16:19:46</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -493,7 +493,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-21 10:02:33</t>
+          <t>2026-03-21 16:19:46</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
